--- a/data/trans_orig/P07B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según salud mental autopercibida en 2023</t>
+          <t>Población según salud mental autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49394</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>30155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40471</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69727</t>
+          <t>71040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199786</t>
+          <t>201259</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>246412</t>
+          <t>245309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145409</t>
+          <t>147261</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>180396</t>
+          <t>180524</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>358139</t>
+          <t>358478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>416579</t>
+          <t>415326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151574</t>
+          <t>151716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196631</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161828</t>
+          <t>164611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200330</t>
+          <t>199769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>324226</t>
+          <t>327686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379817</t>
+          <t>383895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55596</t>
+          <t>55038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92289</t>
+          <t>91968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63939</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91546</t>
+          <t>91642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130117</t>
+          <t>130337</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177199</t>
+          <t>171215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45912</t>
+          <t>44145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>65016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168428</t>
+          <t>171184</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212604</t>
+          <t>213505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143092</t>
+          <t>143093</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177146</t>
+          <t>176708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>323993</t>
+          <t>323747</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>377990</t>
+          <t>377658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147372</t>
+          <t>146299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192292</t>
+          <t>189721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120416</t>
+          <t>119600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152058</t>
+          <t>151996</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>277245</t>
+          <t>279105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332438</t>
+          <t>333023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57802</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95054</t>
+          <t>95902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64333</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106061</t>
+          <t>105548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151271</t>
+          <t>151960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46322</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23982</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66784</t>
+          <t>65980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>294742</t>
+          <t>293717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>586270</t>
+          <t>572609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66744</t>
+          <t>65704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88903</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>372380</t>
+          <t>372118</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>705827</t>
+          <t>674843</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>62920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>249188</t>
+          <t>249636</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66322</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84266</t>
+          <t>102015</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300493</t>
+          <t>300209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88069</t>
+          <t>90257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26960</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104027</t>
+          <t>103567</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,47 +2791,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>9847</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5176</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10218</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45183</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>75628</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78777</t>
+          <t>77884</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81175</t>
+          <t>81106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138881</t>
+          <t>138680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>399768</t>
+          <t>397717</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>468362</t>
+          <t>467087</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>387988</t>
+          <t>387654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>740053</t>
+          <t>702861</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>816620</t>
+          <t>817254</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1227731</t>
+          <t>1291502</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331782</t>
+          <t>335493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>402325</t>
+          <t>401518</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156106</t>
+          <t>167950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>379054</t>
+          <t>380772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>477807</t>
+          <t>463889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>745889</t>
+          <t>747780</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137602</t>
+          <t>139689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>201691</t>
+          <t>207308</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139070</t>
+          <t>139705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>190591</t>
+          <t>185226</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>323326</t>
+          <t>326156</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22054</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32338</t>
+          <t>31700</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>43435</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82381</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>342386</t>
+          <t>328439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111209</t>
+          <t>111138</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>379791</t>
+          <t>365342</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>194240</t>
+          <t>194539</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>240678</t>
+          <t>241146</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>259714</t>
+          <t>290161</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>420830</t>
+          <t>423659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>487112</t>
+          <t>470320</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>643960</t>
+          <t>640192</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>137516</t>
+          <t>137869</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>182171</t>
+          <t>184401</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>158704</t>
+          <t>157535</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>244564</t>
+          <t>247958</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>302941</t>
+          <t>305934</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>415509</t>
+          <t>413554</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>44039</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75292</t>
+          <t>75089</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54365</t>
+          <t>54198</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>204363</t>
+          <t>196729</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>109673</t>
+          <t>110145</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>259270</t>
+          <t>261669</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,47 +4190,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>18464</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>12379</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>28417</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>18464</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>12069</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>27732</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>57054</t>
+          <t>56046</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>83960</t>
+          <t>81548</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>59613</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>88531</t>
+          <t>88677</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>28315</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>67129</t>
+          <t>66829</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>357444</t>
+          <t>357462</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>410191</t>
+          <t>408310</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>396369</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>466547</t>
+          <t>462611</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>59376</t>
+          <t>57253</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>105847</t>
+          <t>106751</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>187058</t>
+          <t>189339</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>234665</t>
+          <t>231710</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>252326</t>
+          <t>254635</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>320142</t>
+          <t>322845</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>79538</t>
+          <t>81470</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>130119</t>
+          <t>134141</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>67199</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>108860</t>
+          <t>108420</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>158516</t>
+          <t>157277</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>237505</t>
+          <t>237407</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>44085</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>59115</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>93176</t>
+          <t>91154</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>131061</t>
+          <t>133185</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>200289</t>
+          <t>201614</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>265740</t>
+          <t>265241</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>609313</t>
+          <t>576911</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>428664</t>
+          <t>430998</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>773628</t>
+          <t>754369</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1383179</t>
+          <t>1386508</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1923414</t>
+          <t>1895944</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1525804</t>
+          <t>1525977</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2032075</t>
+          <t>2015811</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2961895</t>
+          <t>2976035</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3728951</t>
+          <t>3764832</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>879267</t>
+          <t>873204</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1205489</t>
+          <t>1199892</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>886269</t>
+          <t>896756</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1181891</t>
+          <t>1185194</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1910861</t>
+          <t>1877569</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2348585</t>
+          <t>2340263</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>411271</t>
+          <t>421615</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>607097</t>
+          <t>606399</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>351178</t>
+          <t>356168</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>527633</t>
+          <t>525136</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>833850</t>
+          <t>822362</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1075675</t>
+          <t>1069427</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P07B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32271</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50146</t>
+          <t>46804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>33580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>56540</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>43314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71040</t>
+          <t>73791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>223641</t>
+          <t>245500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201259</t>
+          <t>221456</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>245309</t>
+          <t>269597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>163089</t>
+          <t>178381</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>147261</t>
+          <t>157892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>180524</t>
+          <t>196960</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>386730</t>
+          <t>423881</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>358478</t>
+          <t>393974</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>415326</t>
+          <t>453877</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>171987</t>
+          <t>185470</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151716</t>
+          <t>161751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196061</t>
+          <t>209394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>180894</t>
+          <t>194953</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164611</t>
+          <t>176322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199769</t>
+          <t>214175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>352881</t>
+          <t>380424</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327686</t>
+          <t>351253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383895</t>
+          <t>410442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72587</t>
+          <t>80880</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91968</t>
+          <t>99797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77618</t>
+          <t>85837</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64152</t>
+          <t>72439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91642</t>
+          <t>101442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>150205</t>
+          <t>166717</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130337</t>
+          <t>145311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171215</t>
+          <t>191677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>34795</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>46823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48945</t>
+          <t>51480</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>39418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65016</t>
+          <t>66657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>191747</t>
+          <t>207483</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>171184</t>
+          <t>184316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>213505</t>
+          <t>230820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159233</t>
+          <t>176095</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143093</t>
+          <t>158525</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176708</t>
+          <t>194988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>350980</t>
+          <t>383577</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>323747</t>
+          <t>356131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>377658</t>
+          <t>410982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>167432</t>
+          <t>178338</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146299</t>
+          <t>155937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189721</t>
+          <t>202100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>135989</t>
+          <t>152854</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119600</t>
+          <t>135819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151996</t>
+          <t>171333</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>303421</t>
+          <t>331192</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279105</t>
+          <t>301311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>333023</t>
+          <t>361209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75403</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57737</t>
+          <t>63565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95902</t>
+          <t>99696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40207</t>
+          <t>44077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>69694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>126515</t>
+          <t>134514</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105548</t>
+          <t>114009</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151960</t>
+          <t>158327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,67 +2089,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7288</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8125</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4953</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>27582</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>41769</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>26152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65980</t>
+          <t>60060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>436678</t>
+          <t>214726</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>293717</t>
+          <t>193219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>572609</t>
+          <t>237606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77471</t>
+          <t>88198</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65704</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87220</t>
+          <t>100609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>514150</t>
+          <t>302924</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>372118</t>
+          <t>279429</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>674843</t>
+          <t>330664</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>151151</t>
+          <t>165177</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62920</t>
+          <t>145489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>249636</t>
+          <t>186549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54923</t>
+          <t>60965</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>206074</t>
+          <t>226142</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102015</t>
+          <t>201304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300209</t>
+          <t>253168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>61782</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>47122</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90257</t>
+          <t>80039</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>18376</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68216</t>
+          <t>80157</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>63552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103567</t>
+          <t>99443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15641</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23806</t>
+          <t>25650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>58044</t>
+          <t>61551</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45016</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75628</t>
+          <t>79435</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>56845</t>
+          <t>63216</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>50874</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77884</t>
+          <t>78028</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>114889</t>
+          <t>124766</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81106</t>
+          <t>106942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138680</t>
+          <t>147868</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -2997,102 +2997,102 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>431811</t>
+          <t>475858</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>397717</t>
+          <t>442972</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>467087</t>
+          <t>512371</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>42,04%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>45,27%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>355814</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>331959</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>381509</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>41,32%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>831672</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>788275</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>876955</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>41,73%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>45,14%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>519158</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>387654</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>702861</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>53,08%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>39,63%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>71,86%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>950968</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>817254</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1291502</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>47,24%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>366573</t>
+          <t>406566</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>335493</t>
+          <t>370411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>401518</t>
+          <t>439464</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>293136</t>
+          <t>320651</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>167950</t>
+          <t>295377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>380772</t>
+          <t>344278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>659708</t>
+          <t>727217</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>463889</t>
+          <t>686035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>747780</t>
+          <t>772315</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>167925</t>
+          <t>176809</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>148062</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>207308</t>
+          <t>208263</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>103779</t>
+          <t>116105</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>96907</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139705</t>
+          <t>136365</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>271705</t>
+          <t>292915</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>185226</t>
+          <t>258502</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>326156</t>
+          <t>329113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>35045</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>25108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>48154</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>148887</t>
+          <t>89382</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82557</t>
+          <t>75597</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>328439</t>
+          <t>104176</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>181008</t>
+          <t>124428</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>108840</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>365342</t>
+          <t>145378</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>250337</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>194539</t>
+          <t>225163</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>241146</t>
+          <t>275187</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>371315</t>
+          <t>418324</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>290161</t>
+          <t>394411</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>423659</t>
+          <t>443271</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>590061</t>
+          <t>668661</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>470320</t>
+          <t>635386</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>640192</t>
+          <t>703954</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>158499</t>
+          <t>196934</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>137869</t>
+          <t>172479</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>184401</t>
+          <t>222771</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>214790</t>
+          <t>239706</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>157535</t>
+          <t>218284</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>247958</t>
+          <t>260817</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>373289</t>
+          <t>436640</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>305934</t>
+          <t>399075</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>413554</t>
+          <t>467421</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>57494</t>
+          <t>77016</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>60142</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75089</t>
+          <t>99634</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>91416</t>
+          <t>67223</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54198</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>196729</t>
+          <t>83717</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>148910</t>
+          <t>144239</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>110145</t>
+          <t>120643</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>261669</t>
+          <t>170228</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22135</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>15333</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>73484</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56046</t>
+          <t>60259</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>81548</t>
+          <t>88452</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>73125</t>
+          <t>80085</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>59153</t>
+          <t>66178</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>97686</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>33674</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>66829</t>
+          <t>72006</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>383923</t>
+          <t>421141</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>357462</t>
+          <t>393300</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>408310</t>
+          <t>450230</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>430515</t>
+          <t>471011</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>388726</t>
+          <t>437708</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>462611</t>
+          <t>507661</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>79572</t>
+          <t>84367</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>57253</t>
+          <t>62716</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>106751</t>
+          <t>109816</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>209129</t>
+          <t>236602</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>189339</t>
+          <t>209852</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>231710</t>
+          <t>264733</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>288701</t>
+          <t>320970</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>254635</t>
+          <t>289179</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>322845</t>
+          <t>358644</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>105593</t>
+          <t>92526</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>81470</t>
+          <t>68925</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>134141</t>
+          <t>117922</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>85480</t>
+          <t>97136</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>108420</t>
+          <t>123505</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>191073</t>
+          <t>189662</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>157277</t>
+          <t>154747</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>237407</t>
+          <t>225029</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,67 +4817,67 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>34037</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>44085</t>
+          <t>46663</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>47800</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>38061</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>61710</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>43817</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>33968</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>57441</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>75022</t>
+          <t>81837</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>59115</t>
+          <t>67734</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>91154</t>
+          <t>98524</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>169209</t>
+          <t>179948</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>133185</t>
+          <t>155647</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>201614</t>
+          <t>209299</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>345484</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>265241</t>
+          <t>277933</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>576911</t>
+          <t>329616</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>514693</t>
+          <t>483518</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>430998</t>
+          <t>447036</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>754369</t>
+          <t>527405</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1549215</t>
+          <t>1443774</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1386508</t>
+          <t>1382024</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1895944</t>
+          <t>1502664</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1674189</t>
+          <t>1637952</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1525977</t>
+          <t>1584162</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2015811</t>
+          <t>1688446</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3223404</t>
+          <t>3081726</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2976035</t>
+          <t>3002853</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3764832</t>
+          <t>3161899</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1095214</t>
+          <t>1216853</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>873204</t>
+          <t>1157074</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1199892</t>
+          <t>1285349</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1088861</t>
+          <t>1205732</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>896756</t>
+          <t>1154836</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1185194</t>
+          <t>1260660</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2184075</t>
+          <t>2422584</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1877569</t>
+          <t>2347586</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2340263</t>
+          <t>2503279</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>531216</t>
+          <t>567865</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>421615</t>
+          <t>516974</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>606399</t>
+          <t>626232</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>425408</t>
+          <t>440340</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>356168</t>
+          <t>402844</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>525136</t>
+          <t>482668</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>956624</t>
+          <t>1008204</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>822362</t>
+          <t>941424</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1069427</t>
+          <t>1076945</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
